--- a/output/ValueSet-vs-OSLAB-microbiology-report.xlsx
+++ b/output/ValueSet-vs-OSLAB-microbiology-report.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>The OS LAB Microbiology Report value set includes codes for Microbiology reports.</t>
+    <t>The OS LAB Microbiology Report value set includes codes for Microbiology reports, for example URINE - Urine M/C/S.</t>
   </si>
   <si>
     <t>Purpose</t>
